--- a/content/CP1972/CP1972 - definition.xlsx
+++ b/content/CP1972/CP1972 - definition.xlsx
@@ -42,19 +42,19 @@
     <t>Cover page</t>
   </si>
   <si>
-    <t>\CP1972 - Sensors and microcontrollers\CP1972-head.docx</t>
+    <t>\CP1972 - Sensors and microcontrollers\CP1972-Head.docx</t>
   </si>
   <si>
     <t>Contents</t>
   </si>
   <si>
-    <t>\CP1972 - Sensors and microcontrollers\CP1972-cont.docx</t>
+    <t>\CP1972 - Sensors and microcontrollers\CP1972-Cont.docx</t>
   </si>
   <si>
     <t>Preparation</t>
   </si>
   <si>
-    <t>\CP1972 - Sensors and microcontrollers\CP1972-prep.docx</t>
+    <t>\CP1972 - Sensors and microcontrollers\CP1972-Prep.docx</t>
   </si>
   <si>
     <t>Analogue inputs</t>
